--- a/RaidenDemo/文档/配置表/__tables__.xlsx
+++ b/RaidenDemo/文档/配置表/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R10fa69b4c1bc4fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3a93ab1329a483c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -125,7 +125,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="22">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -245,6 +245,21 @@
       <x:color rgb="FF000000"/>
       <x:name val="等线"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF006100"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
   </x:fonts>
   <x:fills count="33">
     <x:fill>
@@ -409,7 +424,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -490,6 +505,20 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -640,7 +669,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -658,6 +687,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -909,322 +977,343 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="2" max="2" width="28.274999618530273" customWidth="1"/>
-    <x:col min="3" max="3" width="31.125" customWidth="1"/>
-    <x:col min="4" max="4" width="32.375" customWidth="1"/>
-    <x:col min="5" max="5" width="26.508333206176758" customWidth="1"/>
-    <x:col min="6" max="6" width="18" customWidth="1"/>
-    <x:col min="7" max="7" width="32.125" customWidth="1"/>
-    <x:col min="8" max="9" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="26.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="49.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="83.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="29.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="51.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="5.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="32.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="16" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="16" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="C1" s="16" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="D1" s="16" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="E1" s="16" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="F1" s="16" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="G1" s="16" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="H1" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="I1" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="J1" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="K1" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="A2" s="16" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="16" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="C2" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="D2" s="16" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="E2" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="F2" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="G2" s="16" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="H2" s="16" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="I2" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="J2" s="17"/>
+      <x:c r="K2" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="16" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="B3" s="17"/>
+      <x:c r="C3" s="17"/>
+      <x:c r="D3" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="E3" s="16" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="F3" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
+      <x:c r="G3" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H3" s="1" t="s">
+      <x:c r="H3" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K3" s="1" t="s">
+      <x:c r="I3" s="17"/>
+      <x:c r="J3" s="17"/>
+      <x:c r="K3" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="B4" t="s">
+      <x:c r="A4" s="17"/>
+      <x:c r="B4" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C4" t="s">
+      <x:c r="C4" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D4" t="b">
+      <x:c r="D4" s="17" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" t="s">
+      <x:c r="E4" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I4" t="s">
+      <x:c r="F4" s="17"/>
+      <x:c r="G4" s="17"/>
+      <x:c r="H4" s="17"/>
+      <x:c r="I4" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="J4" s="17"/>
+      <x:c r="K4" s="17"/>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" t="s">
+      <x:c r="A5" s="17"/>
+      <x:c r="B5" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C5" t="s">
+      <x:c r="C5" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D5" t="b">
+      <x:c r="D5" s="17" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" t="s">
+      <x:c r="E5" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I5" t="s">
+      <x:c r="F5" s="17"/>
+      <x:c r="G5" s="17"/>
+      <x:c r="H5" s="17"/>
+      <x:c r="I5" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="J5" s="17"/>
+      <x:c r="K5" s="17"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6"/>
-      <x:c r="B6" t="str">
+      <x:c r="A6" s="17"/>
+      <x:c r="B6" s="17" t="str">
         <x:v>cfgObj.StageObj</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C6" s="17" t="str">
         <x:v>resource.StageResource</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="D6" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E6" s="17" t="str">
         <x:v>StageResource.xlsx</x:v>
       </x:c>
-      <x:c r="F6"/>
-      <x:c r="G6"/>
-      <x:c r="H6"/>
-      <x:c r="I6" t="str">
+      <x:c r="F6" s="17"/>
+      <x:c r="G6" s="17"/>
+      <x:c r="H6" s="17"/>
+      <x:c r="I6" s="17" t="str">
         <x:v>雷电关卡配置表</x:v>
       </x:c>
-      <x:c r="J6"/>
-      <x:c r="K6"/>
+      <x:c r="J6" s="17"/>
+      <x:c r="K6" s="17"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7" t="str">
+      <x:c r="A7" s="17"/>
+      <x:c r="B7" s="17" t="str">
         <x:v>cfgObj.StageWaveObj</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="17" t="str">
         <x:v>resource.StageWaveResource</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D7" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E7" s="17" t="str">
         <x:v>StageWaveResource.xlsx</x:v>
       </x:c>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7" t="str">
+      <x:c r="F7" s="17"/>
+      <x:c r="G7" s="17"/>
+      <x:c r="H7" s="17"/>
+      <x:c r="I7" s="17" t="str">
         <x:v>雷电关卡波次配置表</x:v>
       </x:c>
-      <x:c r="J7"/>
-      <x:c r="K7"/>
+      <x:c r="J7" s="17"/>
+      <x:c r="K7" s="17"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8" t="str">
+      <x:c r="A8" s="17"/>
+      <x:c r="B8" s="17" t="str">
         <x:v>cfgObj.EnemyObj</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="17" t="str">
         <x:v>resource.EnemyResource</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="D8" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="E8" s="17" t="str">
         <x:v>EnemyResource.xlsx</x:v>
       </x:c>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8" t="str">
+      <x:c r="F8" s="17"/>
+      <x:c r="G8" s="17"/>
+      <x:c r="H8" s="17"/>
+      <x:c r="I8" s="17" t="str">
         <x:v>普通敌机配置表</x:v>
       </x:c>
-      <x:c r="J8"/>
-      <x:c r="K8"/>
+      <x:c r="J8" s="17"/>
+      <x:c r="K8" s="17"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9"/>
-      <x:c r="B9" t="str">
-        <x:v>cfgObj.EnemyBulletObj</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>resource.EnemyBulletResource</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="A9" s="17"/>
+      <x:c r="B9" s="17" t="str">
+        <x:v>cfgObj.PlayerAircraftObj</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>resource.PlayerAircraftResource</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>EnemyBulletResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
-      <x:c r="I9" t="str">
-        <x:v>敌机子弹配置表</x:v>
-      </x:c>
-      <x:c r="J9"/>
-      <x:c r="K9"/>
+      <x:c r="E9" s="17" t="str">
+        <x:v>PlayerAircraftResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="17"/>
+      <x:c r="H9" s="17"/>
+      <x:c r="I9" s="17" t="str">
+        <x:v>玩家飞机类型配置表</x:v>
+      </x:c>
+      <x:c r="J9" s="17"/>
+      <x:c r="K9" s="17"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10"/>
-      <x:c r="B10" t="str">
-        <x:v>cfgObj.PlayerAircraftObj</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>resource.PlayerAircraftResource</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="A10" s="17"/>
+      <x:c r="B10" s="17" t="str">
+        <x:v>cfgObj.PlayerAircraftLevelObj</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>resource.PlayerAircraftLevelResource</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" t="str">
-        <x:v>PlayerAircraftResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-      <x:c r="H10"/>
-      <x:c r="I10" t="str">
-        <x:v>玩家飞机类型配置表</x:v>
-      </x:c>
-      <x:c r="J10"/>
-      <x:c r="K10"/>
+      <x:c r="E10" s="17" t="str">
+        <x:v>PlayerAircraftLevelResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="17"/>
+      <x:c r="H10" s="17"/>
+      <x:c r="I10" s="17" t="str">
+        <x:v>玩家飞机等级配置表</x:v>
+      </x:c>
+      <x:c r="J10" s="17"/>
+      <x:c r="K10" s="17"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11" t="str">
-        <x:v>cfgObj.PlayerAircraftLevelObj</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>resource.PlayerAircraftLevelResource</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="A11" s="17"/>
+      <x:c r="B11" s="17" t="str">
+        <x:v>cfgObj.BulletObj</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>resource.BulletResource</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E11" t="str">
-        <x:v>PlayerAircraftLevelResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-      <x:c r="I11" t="str">
-        <x:v>玩家飞机等级配置表</x:v>
-      </x:c>
-      <x:c r="J11"/>
-      <x:c r="K11"/>
+      <x:c r="E11" s="17" t="str">
+        <x:v>BulletResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="17"/>
+      <x:c r="H11" s="17"/>
+      <x:c r="I11" s="17" t="str">
+        <x:v>通用子弹配置表</x:v>
+      </x:c>
+      <x:c r="J11" s="17"/>
+      <x:c r="K11" s="17"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="3"/>
-      <x:c r="B12" s="3" t="str">
-        <x:v>cfgObj.BulletObj</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="str">
-        <x:v>resource.BulletResource</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="str">
+      <x:c r="A12" s="18"/>
+      <x:c r="B12" s="18" t="str">
+        <x:v>cfgObj.EffectObj</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>resource.EffectResource</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E12" s="3" t="str">
-        <x:v>BulletResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F12" s="3"/>
-      <x:c r="G12" s="3"/>
-      <x:c r="H12" s="3"/>
-      <x:c r="I12" s="3" t="str">
-        <x:v>通用子弹配置表</x:v>
-      </x:c>
-      <x:c r="J12" s="3"/>
-      <x:c r="K12" s="3"/>
+      <x:c r="E12" s="18" t="str">
+        <x:v>EffectResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F12" s="18"/>
+      <x:c r="G12" s="18"/>
+      <x:c r="H12" s="18"/>
+      <x:c r="I12" s="18" t="str">
+        <x:v>通用特效配置表</x:v>
+      </x:c>
+      <x:c r="J12" s="18"/>
+      <x:c r="K12" s="18"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="5"/>
-      <x:c r="B13" s="5" t="str">
-        <x:v>cfgObj.EffectObj</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>resource.EffectResource</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="str">
+      <x:c r="A13" s="17"/>
+      <x:c r="B13" s="17" t="str">
+        <x:v>cfgObj.SceneBgObj</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>resource.SceneBgResource</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E13" s="5" t="str">
-        <x:v>EffectResource.xlsx</x:v>
-      </x:c>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="5" t="str">
-        <x:v>通用特效配置表</x:v>
-      </x:c>
-      <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
+      <x:c r="E13" s="17" t="str">
+        <x:v>SceneBgResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F13" s="17"/>
+      <x:c r="G13" s="17"/>
+      <x:c r="H13" s="17"/>
+      <x:c r="I13" s="17" t="str">
+        <x:v>场景背景配置表</x:v>
+      </x:c>
+      <x:c r="J13" s="17"/>
+      <x:c r="K13" s="17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RaidenDemo/文档/配置表/__tables__.xlsx
+++ b/RaidenDemo/文档/配置表/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3a93ab1329a483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b3bcf1ef6854400"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -261,7 +261,7 @@
       <x:name val="微软雅黑"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -421,6 +421,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -669,7 +674,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -726,6 +731,69 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -780,6 +848,23 @@
     <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1315,6 +1400,29 @@
       <x:c r="J13" s="17"/>
       <x:c r="K13" s="17"/>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="28"/>
+      <x:c r="B14" s="28" t="str">
+        <x:v>cfgObj.StageItemObj</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="str">
+        <x:v>resource.StageItemResource</x:v>
+      </x:c>
+      <x:c r="D14" s="29" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="str">
+        <x:v>StageItemResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F14" s="28"/>
+      <x:c r="G14" s="28"/>
+      <x:c r="H14" s="28"/>
+      <x:c r="I14" s="28" t="str">
+        <x:v>关卡道具配置表</x:v>
+      </x:c>
+      <x:c r="J14" s="28"/>
+      <x:c r="K14" s="28"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/RaidenDemo/文档/配置表/__tables__.xlsx
+++ b/RaidenDemo/文档/配置表/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b3bcf1ef6854400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R48eb237e7aba4128"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,7 +674,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -789,6 +789,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -1423,6 +1431,29 @@
       <x:c r="J14" s="28"/>
       <x:c r="K14" s="28"/>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="9"/>
+      <x:c r="B15" s="9" t="str">
+        <x:v>cfgObj.WingmanObj</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>resource.WingmanResource</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="str">
+        <x:v>WingmanResource.xlsx</x:v>
+      </x:c>
+      <x:c r="F15" s="9"/>
+      <x:c r="G15" s="9"/>
+      <x:c r="H15" s="9"/>
+      <x:c r="I15" s="9" t="str">
+        <x:v>僚机类型配置表</x:v>
+      </x:c>
+      <x:c r="J15" s="9"/>
+      <x:c r="K15" s="9"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
